--- a/lab1/MyDrinkShop/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/lab1/MyDrinkShop/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet name="Coding Phase Defects" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tool-basedCodeAnalysis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
@@ -19,57 +19,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t xml:space="preserve">do not print this form</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>do not print this form</t>
   </si>
   <si>
     <t>Echipa</t>
   </si>
   <si>
-    <t xml:space="preserve">Review Form. Requirements Defects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numele si prenumele</t>
+    <t>Review Form. Requirements Defects</t>
+  </si>
+  <si>
+    <t>Numele si prenumele</t>
   </si>
   <si>
     <t>Grupa</t>
   </si>
   <si>
-    <t xml:space="preserve">Student 1:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pastin Maria-Ivona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document  Title:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirements Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student 2:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pecsar Stefania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Author Name:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firicescu George</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student 3:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popoviciu Luca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewer Name:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pastin Maria</t>
+    <t>Student 1:</t>
+  </si>
+  <si>
+    <t>Pastin Maria-Ivona</t>
+  </si>
+  <si>
+    <t>Document  Title:</t>
+  </si>
+  <si>
+    <t>Requirements Document</t>
+  </si>
+  <si>
+    <t>Student 2:</t>
+  </si>
+  <si>
+    <t>Pecsar Stefania</t>
+  </si>
+  <si>
+    <t>Author Name:</t>
+  </si>
+  <si>
+    <t>Firicescu George</t>
+  </si>
+  <si>
+    <t>Student 3:</t>
+  </si>
+  <si>
+    <t>Popoviciu Luca</t>
+  </si>
+  <si>
+    <t>Reviewer Name:</t>
+  </si>
+  <si>
+    <t>Pastin Maria</t>
   </si>
   <si>
     <t xml:space="preserve">Review date: </t>
@@ -78,55 +78,55 @@
     <t>1.03.2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Crt. No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checked Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doc. page/line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comments/ improvements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effort to review document (hours):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Form. Architectural Design Defects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architectural Design Document</t>
+    <t>Crt. No.</t>
+  </si>
+  <si>
+    <t>Checked Item</t>
+  </si>
+  <si>
+    <t>Doc. page/line</t>
+  </si>
+  <si>
+    <t>Comments/ improvements</t>
+  </si>
+  <si>
+    <t>Effort to review document (hours):</t>
+  </si>
+  <si>
+    <t>Review Form. Architectural Design Defects</t>
+  </si>
+  <si>
+    <t>Architectural Design Document</t>
   </si>
   <si>
     <t xml:space="preserve">Author Name: </t>
   </si>
   <si>
-    <t xml:space="preserve">Georgescu Anca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Form. Coding Defects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popescu Ionel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pastin Maria, Pecsar Stefania, Popoviciu Luca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tool-based Code Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tool used:</t>
+    <t>Georgescu Anca</t>
+  </si>
+  <si>
+    <t>Review Form. Coding Defects</t>
+  </si>
+  <si>
+    <t>Coding Document</t>
+  </si>
+  <si>
+    <t>Popescu Ionel</t>
+  </si>
+  <si>
+    <t>Pastin Maria, Pecsar Stefania, Popoviciu Luca</t>
+  </si>
+  <si>
+    <t>Tool-based Code Analysis</t>
+  </si>
+  <si>
+    <t>Tool used:</t>
   </si>
   <si>
     <t>SonarQube</t>
   </si>
   <si>
-    <t xml:space="preserve">File, Line</t>
+    <t>File, Line</t>
   </si>
   <si>
     <t>Issue</t>
@@ -138,14 +138,91 @@
     <t>After/Argument</t>
   </si>
   <si>
-    <t xml:space="preserve">Effort to perform tool-based code analysis (hours):</t>
+    <t>Effort to perform tool-based code analysis (hours):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Calculul totalului zilei nu este vizibil intr-o clasa speciala/dedicata</t>
+  </si>
+  <si>
+    <r>
+      <t>Observer Pattern</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Segoe UI"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <vertAlign val="baseline"/>
+      </rPr>
+      <t>ar putea notifica StocServiceautomat la finalizarea unei comenzi</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Segoe UI"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <vertAlign val="baseline"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Observer Pattern ar trebui sa notifice stocul la finalizarea unei comenzi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observer Pattern ar trebui sa notifice stocul la finalizarea unei comenzi. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observer Pattern ar trebui sa notifice stocul la finalizarea unei comenzi.               Repository Pattern e deja utilizat conform cerintelor.       Strategy Pattern ar fi util pentru formatele de export CSV/txt                                                    </t>
+  </si>
+  <si>
+    <t>Single Responsability Principle unde se gestioneaza direct listele de entitati(reteta, product) incalcand separarea responsabilitatilor</t>
+  </si>
+  <si>
+    <t>Nu exista o relatie directa intre product si reteta in diagrama</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -188,6 +265,18 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+      <color rgb="FF000000"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -212,7 +301,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -281,11 +370,25 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -355,6 +458,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1" xfId="0">
+      <alignment wrapText="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1" xfId="0">
+      <alignment wrapText="1" horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -882,11 +995,12 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" style="1" width="8.90625"/>
     <col customWidth="1" min="2" max="2" style="1" width="12.26953125"/>
-    <col customWidth="1" min="3" max="4" style="1" width="16.26953125"/>
+    <col customWidth="1" min="3" max="3" style="1" width="16.26953125"/>
+    <col customWidth="1" min="4" max="4" style="1" width="16.26953125"/>
     <col customWidth="1" min="5" max="5" style="1" width="41.453125"/>
     <col min="6" max="8" style="1" width="8.90625"/>
     <col customWidth="1" min="9" max="9" style="1" width="21"/>
@@ -1010,7 +1124,7 @@
     </row>
     <row r="11">
       <c r="B11" s="6">
-        <f t="shared" ref="B11:B25" si="0">B10+1</f>
+        <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="17"/>
@@ -1019,7 +1133,7 @@
     </row>
     <row r="12">
       <c r="B12" s="6">
-        <f t="shared" si="0"/>
+        <f>B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="17"/>
@@ -1028,7 +1142,7 @@
     </row>
     <row r="13">
       <c r="B13" s="6">
-        <f t="shared" si="0"/>
+        <f>B12+1</f>
         <v>4</v>
       </c>
       <c r="C13" s="17"/>
@@ -1037,7 +1151,7 @@
     </row>
     <row r="14">
       <c r="B14" s="6">
-        <f t="shared" si="0"/>
+        <f>B13+1</f>
         <v>5</v>
       </c>
       <c r="C14" s="17"/>
@@ -1046,7 +1160,7 @@
     </row>
     <row r="15">
       <c r="B15" s="6">
-        <f t="shared" si="0"/>
+        <f>B14+1</f>
         <v>6</v>
       </c>
       <c r="C15" s="17"/>
@@ -1055,7 +1169,7 @@
     </row>
     <row r="16">
       <c r="B16" s="6">
-        <f t="shared" si="0"/>
+        <f>B15+1</f>
         <v>7</v>
       </c>
       <c r="C16" s="17"/>
@@ -1064,7 +1178,7 @@
     </row>
     <row r="17">
       <c r="B17" s="6">
-        <f t="shared" si="0"/>
+        <f>B16+1</f>
         <v>8</v>
       </c>
       <c r="C17" s="17"/>
@@ -1073,7 +1187,7 @@
     </row>
     <row r="18">
       <c r="B18" s="6">
-        <f t="shared" si="0"/>
+        <f>B17+1</f>
         <v>9</v>
       </c>
       <c r="C18" s="6"/>
@@ -1082,7 +1196,7 @@
     </row>
     <row r="19">
       <c r="B19" s="6">
-        <f t="shared" si="0"/>
+        <f>B18+1</f>
         <v>10</v>
       </c>
       <c r="C19" s="6"/>
@@ -1091,7 +1205,7 @@
     </row>
     <row r="20">
       <c r="B20" s="6">
-        <f t="shared" si="0"/>
+        <f>B19+1</f>
         <v>11</v>
       </c>
       <c r="C20" s="6"/>
@@ -1100,7 +1214,7 @@
     </row>
     <row r="21">
       <c r="B21" s="6">
-        <f t="shared" si="0"/>
+        <f>B20+1</f>
         <v>12</v>
       </c>
       <c r="C21" s="6"/>
@@ -1109,7 +1223,7 @@
     </row>
     <row r="22">
       <c r="B22" s="6">
-        <f t="shared" si="0"/>
+        <f>B21+1</f>
         <v>13</v>
       </c>
       <c r="C22" s="6"/>
@@ -1118,7 +1232,7 @@
     </row>
     <row r="23">
       <c r="B23" s="6">
-        <f t="shared" si="0"/>
+        <f>B22+1</f>
         <v>14</v>
       </c>
       <c r="C23" s="6"/>
@@ -1127,7 +1241,7 @@
     </row>
     <row r="24">
       <c r="B24" s="6">
-        <f t="shared" si="0"/>
+        <f>B23+1</f>
         <v>15</v>
       </c>
       <c r="C24" s="6"/>
@@ -1136,7 +1250,7 @@
     </row>
     <row r="25">
       <c r="B25" s="6">
-        <f t="shared" si="0"/>
+        <f>B24+1</f>
         <v>16</v>
       </c>
       <c r="C25" s="6"/>
@@ -1173,18 +1287,19 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" style="1" width="8.90625"/>
     <col customWidth="1" min="2" max="2" style="1" width="12.26953125"/>
-    <col customWidth="1" min="3" max="4" style="1" width="16.26953125"/>
+    <col customWidth="1" min="3" max="3" style="1" width="16.26953125"/>
+    <col customWidth="1" min="4" max="4" style="1" width="16.26953125"/>
     <col customWidth="1" min="5" max="5" style="1" width="41.453125"/>
     <col min="6" max="8" style="1" width="8.90625"/>
     <col customWidth="1" min="9" max="9" style="1" width="22.08984375"/>
     <col min="10" max="16384" style="1" width="8.90625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5">
+    <row r="1" ht="15">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1290,155 +1405,195 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15">
       <c r="B10" s="6">
         <v>1</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="11">
+      <c r="C10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" ht="15">
       <c r="B11" s="6">
-        <f t="shared" ref="B11:B26" si="1">B10+1</f>
+        <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="34"/>
+      <c r="E11" s="36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" ht="28.5">
       <c r="B12" s="6">
-        <f t="shared" si="1"/>
+        <f>B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-    </row>
-    <row r="13">
+      <c r="C12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" ht="15">
       <c r="B13" s="6">
-        <f t="shared" si="1"/>
+        <f>B12+1</f>
         <v>4</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-    </row>
-    <row r="14">
+      <c r="C13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" ht="15">
       <c r="B14" s="6">
-        <f t="shared" si="1"/>
+        <f>B13+1</f>
         <v>5</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="34"/>
+      <c r="E14" s="36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" ht="69">
       <c r="B15" s="6">
-        <f t="shared" si="1"/>
+        <f>B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" ht="15">
       <c r="B16" s="6">
-        <f t="shared" si="1"/>
+        <f>B15+1</f>
         <v>7</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" ht="42">
       <c r="B17" s="6">
-        <f t="shared" si="1"/>
+        <f>B16+1</f>
         <v>8</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="34"/>
+      <c r="E17" s="36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" ht="15">
       <c r="B18" s="6">
-        <f t="shared" si="1"/>
+        <f>B17+1</f>
         <v>9</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" ht="28.5">
       <c r="B19" s="6">
-        <f t="shared" si="1"/>
+        <f>B18+1</f>
         <v>10</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="34"/>
+      <c r="E19" s="36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" ht="15">
       <c r="B20" s="6">
-        <f t="shared" si="1"/>
+        <f>B19+1</f>
         <v>11</v>
       </c>
-      <c r="C20" s="17"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="17"/>
       <c r="E20" s="18"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15">
       <c r="B21" s="6">
-        <f t="shared" si="1"/>
+        <f>B20+1</f>
         <v>12</v>
       </c>
-      <c r="C21" s="17"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="17"/>
       <c r="E21" s="18"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15">
       <c r="B22" s="6">
-        <f t="shared" si="1"/>
+        <f>B21+1</f>
         <v>13</v>
       </c>
-      <c r="C22" s="17"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="17"/>
       <c r="E22" s="18"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15">
       <c r="B23" s="6">
-        <f t="shared" si="1"/>
+        <f>B22+1</f>
         <v>14</v>
       </c>
-      <c r="C23" s="17"/>
+      <c r="C23" s="4"/>
       <c r="D23" s="17"/>
       <c r="E23" s="18"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15">
       <c r="B24" s="6">
-        <f t="shared" si="1"/>
+        <f>B23+1</f>
         <v>15</v>
       </c>
-      <c r="C24" s="17"/>
+      <c r="C24" s="4"/>
       <c r="D24" s="17"/>
       <c r="E24" s="18"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15">
       <c r="B25" s="6">
-        <f t="shared" si="1"/>
+        <f>B24+1</f>
         <v>16</v>
       </c>
-      <c r="C25" s="17"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="17"/>
       <c r="E25" s="18"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15">
       <c r="B26" s="6">
-        <f t="shared" si="1"/>
+        <f>B25+1</f>
         <v>17</v>
       </c>
-      <c r="C26" s="17"/>
+      <c r="C26" s="4"/>
       <c r="D26" s="17"/>
       <c r="E26" s="18"/>
     </row>
@@ -1454,9 +1609,9 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1472,7 +1627,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" style="1" width="8.90625"/>
     <col customWidth="1" min="2" max="2" style="1" width="12.26953125"/>
@@ -1484,7 +1639,7 @@
     <col min="10" max="16384" style="1" width="8.90625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5">
+    <row r="1" ht="15">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1600,7 +1755,7 @@
     </row>
     <row r="11">
       <c r="B11" s="6">
-        <f t="shared" ref="B11:B30" si="2">B10+1</f>
+        <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="17"/>
@@ -1609,7 +1764,7 @@
     </row>
     <row r="12">
       <c r="B12" s="6">
-        <f t="shared" si="2"/>
+        <f>B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="17"/>
@@ -1618,7 +1773,7 @@
     </row>
     <row r="13">
       <c r="B13" s="6">
-        <f t="shared" si="2"/>
+        <f>B12+1</f>
         <v>4</v>
       </c>
       <c r="C13" s="17"/>
@@ -1627,7 +1782,7 @@
     </row>
     <row r="14">
       <c r="B14" s="6">
-        <f t="shared" si="2"/>
+        <f>B13+1</f>
         <v>5</v>
       </c>
       <c r="C14" s="17"/>
@@ -1636,7 +1791,7 @@
     </row>
     <row r="15">
       <c r="B15" s="6">
-        <f t="shared" si="2"/>
+        <f>B14+1</f>
         <v>6</v>
       </c>
       <c r="C15" s="17"/>
@@ -1645,7 +1800,7 @@
     </row>
     <row r="16">
       <c r="B16" s="6">
-        <f t="shared" si="2"/>
+        <f>B15+1</f>
         <v>7</v>
       </c>
       <c r="C16" s="17"/>
@@ -1654,7 +1809,7 @@
     </row>
     <row r="17">
       <c r="B17" s="6">
-        <f t="shared" si="2"/>
+        <f>B16+1</f>
         <v>8</v>
       </c>
       <c r="C17" s="17"/>
@@ -1663,7 +1818,7 @@
     </row>
     <row r="18">
       <c r="B18" s="6">
-        <f t="shared" si="2"/>
+        <f>B17+1</f>
         <v>9</v>
       </c>
       <c r="C18" s="17"/>
@@ -1672,7 +1827,7 @@
     </row>
     <row r="19">
       <c r="B19" s="6">
-        <f t="shared" si="2"/>
+        <f>B18+1</f>
         <v>10</v>
       </c>
       <c r="C19" s="17"/>
@@ -1681,7 +1836,7 @@
     </row>
     <row r="20">
       <c r="B20" s="6">
-        <f t="shared" si="2"/>
+        <f>B19+1</f>
         <v>11</v>
       </c>
       <c r="C20" s="17"/>
@@ -1690,7 +1845,7 @@
     </row>
     <row r="21">
       <c r="B21" s="6">
-        <f t="shared" si="2"/>
+        <f>B20+1</f>
         <v>12</v>
       </c>
       <c r="C21" s="17"/>
@@ -1699,7 +1854,7 @@
     </row>
     <row r="22">
       <c r="B22" s="6">
-        <f t="shared" si="2"/>
+        <f>B21+1</f>
         <v>13</v>
       </c>
       <c r="C22" s="17"/>
@@ -1708,7 +1863,7 @@
     </row>
     <row r="23">
       <c r="B23" s="6">
-        <f t="shared" si="2"/>
+        <f>B22+1</f>
         <v>14</v>
       </c>
       <c r="C23" s="17"/>
@@ -1717,7 +1872,7 @@
     </row>
     <row r="24">
       <c r="B24" s="6">
-        <f t="shared" si="2"/>
+        <f>B23+1</f>
         <v>15</v>
       </c>
       <c r="C24" s="17"/>
@@ -1726,7 +1881,7 @@
     </row>
     <row r="25">
       <c r="B25" s="6">
-        <f t="shared" si="2"/>
+        <f>B24+1</f>
         <v>16</v>
       </c>
       <c r="C25" s="17"/>
@@ -1735,7 +1890,7 @@
     </row>
     <row r="26">
       <c r="B26" s="6">
-        <f t="shared" si="2"/>
+        <f>B25+1</f>
         <v>17</v>
       </c>
       <c r="C26" s="17"/>
@@ -1744,7 +1899,7 @@
     </row>
     <row r="27">
       <c r="B27" s="6">
-        <f t="shared" si="2"/>
+        <f>B26+1</f>
         <v>18</v>
       </c>
       <c r="C27" s="17"/>
@@ -1753,7 +1908,7 @@
     </row>
     <row r="28">
       <c r="B28" s="6">
-        <f t="shared" si="2"/>
+        <f>B27+1</f>
         <v>19</v>
       </c>
       <c r="C28" s="17"/>
@@ -1762,7 +1917,7 @@
     </row>
     <row r="29">
       <c r="B29" s="6">
-        <f t="shared" si="2"/>
+        <f>B28+1</f>
         <v>20</v>
       </c>
       <c r="C29" s="17"/>
@@ -1771,7 +1926,7 @@
     </row>
     <row r="30">
       <c r="B30" s="6">
-        <f t="shared" si="2"/>
+        <f>B29+1</f>
         <v>21</v>
       </c>
       <c r="C30" s="17"/>
@@ -1787,12 +1942,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1808,7 +1963,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" style="1" width="8.90625"/>
     <col customWidth="1" min="2" max="2" style="1" width="12.26953125"/>
@@ -1821,7 +1976,7 @@
     <col min="10" max="16384" style="1" width="8.90625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5">
+    <row r="1" ht="15">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1933,7 +2088,7 @@
     </row>
     <row r="11">
       <c r="B11" s="6">
-        <f t="shared" ref="B11:B30" si="3">B10+1</f>
+        <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="17"/>
@@ -1943,7 +2098,7 @@
     </row>
     <row r="12">
       <c r="B12" s="6">
-        <f t="shared" si="3"/>
+        <f>B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="17"/>
@@ -1953,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="B13" s="6">
-        <f t="shared" si="3"/>
+        <f>B12+1</f>
         <v>4</v>
       </c>
       <c r="C13" s="17"/>
@@ -1963,7 +2118,7 @@
     </row>
     <row r="14">
       <c r="B14" s="6">
-        <f t="shared" si="3"/>
+        <f>B13+1</f>
         <v>5</v>
       </c>
       <c r="C14" s="17"/>
@@ -1973,7 +2128,7 @@
     </row>
     <row r="15">
       <c r="B15" s="6">
-        <f t="shared" si="3"/>
+        <f>B14+1</f>
         <v>6</v>
       </c>
       <c r="C15" s="17"/>
@@ -1983,7 +2138,7 @@
     </row>
     <row r="16">
       <c r="B16" s="6">
-        <f t="shared" si="3"/>
+        <f>B15+1</f>
         <v>7</v>
       </c>
       <c r="C16" s="17"/>
@@ -1993,7 +2148,7 @@
     </row>
     <row r="17">
       <c r="B17" s="6">
-        <f t="shared" si="3"/>
+        <f>B16+1</f>
         <v>8</v>
       </c>
       <c r="C17" s="17"/>
@@ -2003,7 +2158,7 @@
     </row>
     <row r="18">
       <c r="B18" s="6">
-        <f t="shared" si="3"/>
+        <f>B17+1</f>
         <v>9</v>
       </c>
       <c r="C18" s="17"/>
@@ -2013,7 +2168,7 @@
     </row>
     <row r="19">
       <c r="B19" s="6">
-        <f t="shared" si="3"/>
+        <f>B18+1</f>
         <v>10</v>
       </c>
       <c r="C19" s="17"/>
@@ -2023,7 +2178,7 @@
     </row>
     <row r="20">
       <c r="B20" s="6">
-        <f t="shared" si="3"/>
+        <f>B19+1</f>
         <v>11</v>
       </c>
       <c r="C20" s="17"/>
@@ -2033,7 +2188,7 @@
     </row>
     <row r="21">
       <c r="B21" s="6">
-        <f t="shared" si="3"/>
+        <f>B20+1</f>
         <v>12</v>
       </c>
       <c r="C21" s="17"/>
@@ -2043,7 +2198,7 @@
     </row>
     <row r="22">
       <c r="B22" s="6">
-        <f t="shared" si="3"/>
+        <f>B21+1</f>
         <v>13</v>
       </c>
       <c r="C22" s="17"/>
@@ -2053,7 +2208,7 @@
     </row>
     <row r="23">
       <c r="B23" s="6">
-        <f t="shared" si="3"/>
+        <f>B22+1</f>
         <v>14</v>
       </c>
       <c r="C23" s="17"/>
@@ -2063,7 +2218,7 @@
     </row>
     <row r="24">
       <c r="B24" s="6">
-        <f t="shared" si="3"/>
+        <f>B23+1</f>
         <v>15</v>
       </c>
       <c r="C24" s="17"/>
@@ -2073,7 +2228,7 @@
     </row>
     <row r="25">
       <c r="B25" s="6">
-        <f t="shared" si="3"/>
+        <f>B24+1</f>
         <v>16</v>
       </c>
       <c r="C25" s="17"/>
@@ -2083,7 +2238,7 @@
     </row>
     <row r="26">
       <c r="B26" s="6">
-        <f t="shared" si="3"/>
+        <f>B25+1</f>
         <v>17</v>
       </c>
       <c r="C26" s="17"/>
@@ -2093,7 +2248,7 @@
     </row>
     <row r="27">
       <c r="B27" s="6">
-        <f t="shared" si="3"/>
+        <f>B26+1</f>
         <v>18</v>
       </c>
       <c r="C27" s="17"/>
@@ -2103,7 +2258,7 @@
     </row>
     <row r="28">
       <c r="B28" s="6">
-        <f t="shared" si="3"/>
+        <f>B27+1</f>
         <v>19</v>
       </c>
       <c r="C28" s="17"/>
@@ -2113,7 +2268,7 @@
     </row>
     <row r="29">
       <c r="B29" s="6">
-        <f t="shared" si="3"/>
+        <f>B28+1</f>
         <v>20</v>
       </c>
       <c r="C29" s="17"/>
@@ -2123,7 +2278,7 @@
     </row>
     <row r="30">
       <c r="B30" s="6">
-        <f t="shared" si="3"/>
+        <f>B29+1</f>
         <v>21</v>
       </c>
       <c r="C30" s="17"/>
@@ -2144,12 +2299,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C32:E32"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
+    <mergeCell ref="C32:E32"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
